--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>131113864</v>
       </c>
       <c r="B4" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>131113864</v>
       </c>
       <c r="B4" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>131113864</v>
       </c>
       <c r="B4" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>131113864</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>131113864</v>
       </c>
       <c r="B4" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -936,7 +936,7 @@
         <v>131113864</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61957350</v>
+        <v>61957347</v>
       </c>
       <c r="B2" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -719,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 14, Vb</t>
+          <t>Finnforsån Lokal 11, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754047.6541896289</v>
+        <v>754254</v>
       </c>
       <c r="R2" t="n">
-        <v>7191480.583975228</v>
+        <v>7191321</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -756,24 +751,14 @@
           <t>2012-09-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lokal 14. Längd= 16,5m. Bredd= 2,6m. Antal levande= 185 st. Antal döda= 0 st. Minsta mussla= 56mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
+          <t>Lokal 11. Längd= 14,5m. Bredd= 1,7m. Antal levande= 1279 st. Antal döda= 1 st. Minsta mussla= Info saknas. Mörkt i vattnet gjorde det svårt att se För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61957349</v>
+        <v>61957348</v>
       </c>
       <c r="B3" t="n">
-        <v>59188</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>60492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>472</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -848,14 +828,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnforsån Lokal 13, Vb</t>
+          <t>Finnforsån Lokal 12, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754086.9151720335</v>
+        <v>754167</v>
       </c>
       <c r="R3" t="n">
-        <v>7191453.025035163</v>
+        <v>7191419</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -885,24 +865,14 @@
           <t>2012-09-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lokal 13. Längd= 15,5m. Bredd= 2,7m. Antal levande= 78 st. Antal döda= 0 st. Minsta mussla= 68mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
+          <t>Lokal 12. Längd= 14,5m. Bredd= 2,4m. Antal levande= 472 st. Antal döda= 0 st. Minsta mussla= Info saknas.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,45 +903,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131113864</v>
+        <v>61957349</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>60492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>101268</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flodpärlmussla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Margaritifera margaritifera</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnforsån, Finnforsån, Vb</t>
+          <t>Finnforsån Lokal 13, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754134</v>
+        <v>754087</v>
       </c>
       <c r="R4" t="n">
-        <v>7191377</v>
+        <v>7191453</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -998,12 +976,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2012-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2012-09-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lokal 13. Längd= 15,5m. Bredd= 2,7m. Antal levande= 78 st. Antal döda= 0 st. Minsta mussla= 68mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,15 +1001,662 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Miljöövervakning flodpärlmussla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>61957350</v>
+      </c>
+      <c r="B5" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 14, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>754048</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7191481</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-09-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lokal 14. Längd= 16,5m. Bredd= 2,6m. Antal levande= 185 st. Antal döda= 0 st. Minsta mussla= 56mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Miljöövervakning flodpärlmussla</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>61957351</v>
+      </c>
+      <c r="B6" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 15, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>754018</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7191507</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-09-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lokal 15. Längd= 14m. Bredd= 3,2m. Antal levande= 182 st. Antal döda= 3 st. Minsta mussla= 46mm.  För mer info kontakta Länsstyrelsen Västerbotten.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Miljöövervakning flodpärlmussla</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>61981833</v>
+      </c>
+      <c r="B7" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 3, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>754126</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7191458</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lokal 3. Längd= 15m. Bredd= 2,8m. Antal levande= 152 st. Antal döda= 1 st. Minsta mussla= 71 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>61981835</v>
+      </c>
+      <c r="B8" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 2, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>754055</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7191491</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lokal 2. Längd= 15m. Bredd= 2,3m. Antal levande= 133 st. Antal döda= 0 st. Minsta mussla= 53 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>61981837</v>
+      </c>
+      <c r="B9" t="n">
+        <v>60492</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101268</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Margaritifera margaritifera</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Finnforsån Lokal 1, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>754033</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7191512</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2006-12-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lokal 1. Längd= 15m. Bredd= 3m. Antal levande= 26 st. Antal döda= 5 st. Minsta mussla= 43 mm. Kontakta Länsstyrelsen Västerboten för mer information.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131113864</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Finnforsån, Finnforsån, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>754134</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7191377</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Emelie Bergkvist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Emelie Bergkvist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41087-2023 artfynd.xlsx
+++ b/artfynd/A 41087-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -786,6 +791,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957347</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957349</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957350</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Miljöövervakning flodpärlmussla</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61957351</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981833</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981835</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61981837</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,8 +1702,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131113864</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>